--- a/seguimiento-modulos/Seguimiento_Nuevos_Modulos_V2_Dashboard.xlsx
+++ b/seguimiento-modulos/Seguimiento_Nuevos_Modulos_V2_Dashboard.xlsx
@@ -14,18 +14,29 @@
     <sheet name="Req. AutoAtención" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Req. RAD" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Req. LM" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Otros Módulos" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Tablas y Glosario" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Req. Calificaciones" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Req. FORCAP" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Req. Portal" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Req. VALS" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Tablas y Glosario" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">Etapas!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Etapas!$A$1:$Q$295</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'Req. AutoAtención'!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. AutoAtención'!$A$1:$O$71</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">'Req. Calificaciones'!$1:$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. Calificaciones'!$A$1:$K$44</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Titles" vbProcedure="false">'Req. FORCAP'!$1:$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. FORCAP'!$A$1:$K$1</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">'Req. LM'!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. LM'!$A$1:$L$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Titles" vbProcedure="false">'Req. Portal'!$1:$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. Portal'!$A$1:$K$1</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Req. RAD'!$1:$1</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. RAD'!$A$1:$K$88</definedName>
+    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Titles" vbProcedure="false">'Req. VALS'!$1:$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'Req. VALS'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,18 +48,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5244" uniqueCount="880">
   <si>
     <t xml:space="preserve">Estado de Avance — Nuevos Módulos SIRH</t>
   </si>
   <si>
-    <t xml:space="preserve">ESTADO GENERAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAZOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVANCE</t>
+    <t xml:space="preserve">🚦  ESTADO GENERAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⏱️  PLAZOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📈  AVANCE</t>
   </si>
   <si>
     <t xml:space="preserve">Indicadores clave</t>
@@ -81,13 +92,13 @@
     <t xml:space="preserve">Requerimientos + actividades</t>
   </si>
   <si>
-    <t xml:space="preserve">Avance de actividades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requerimientos — Listos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requerimientos — Listos + Maqueta</t>
+    <t xml:space="preserve">🗂️  Avance de actividades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📦  Requerimientos — Listos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧩  Requerimientos — Listos + Maqueta</t>
   </si>
   <si>
     <t xml:space="preserve">Avance por Etapa</t>
@@ -117,13 +128,13 @@
     <t xml:space="preserve">Componentes destacados</t>
   </si>
   <si>
-    <t xml:space="preserve">Mejor avance:</t>
+    <t xml:space="preserve">🏆 Mejor avance:</t>
   </si>
   <si>
     <t xml:space="preserve">% avance:</t>
   </si>
   <si>
-    <t xml:space="preserve">Menor avance:</t>
+    <t xml:space="preserve">⚠️ Menor avance:</t>
   </si>
   <si>
     <t xml:space="preserve">Notas de esta versión: se corrigió la fórmula de Estado en la hoja Etapas (la referencia a 'Tablas y Glosario'!F1 no estaba anclada con $, por lo que cada fila comparaba contra una celda de fecha distinta y en su mayoría vacía) y la fórmula de desglose por Responsable en Indicadores (las columnas C:J referenciaban columnas incorrectas de Etapas). Los gráficos dinámicos originales (basados en tablas dinámicas) se reemplazaron por gráficos nativos con fórmulas para mayor estabilidad y compatibilidad.</t>
@@ -2259,22 +2270,205 @@
 - Emitir informe que permita seguimiento de los oficios y los pronunciamientos de la COMPIN asociados. </t>
   </si>
   <si>
-    <t xml:space="preserve">Módulos sin requerimientos cargados todavía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los módulos Calificaciones, FORCAP, Portal SIRH y VALS aún no registran su detalle de requerimientos en el archivo de origen (hojas vacías). Sus actividades de cronograma sí están incluidas en la hoja Etapas y en los indicadores generales del Dashboard. Esta hoja se completará en cuanto el equipo cargue el detalle de requerimientos de cada módulo, replicando la estructura de las hojas Req. AutoAtención / Req. RAD / Req. LM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○  Calificaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○  FORCAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○  Portal SIRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○  VALS</t>
+    <t xml:space="preserve">Proceso Calificatorio Ley 18.834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confeccionar listado de miembros de la junta calificadora </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-02 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir resolución de la junta calificadora </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar y acceder a antecedentes para diseñar y programar el proceso calificatorio (Nómina de Integrantes Junta Calificadora por Estamento, Normativa Vigente, Nómina de Personal con Requisito Calificación, Parámetros calificatorios y coeficientes)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir informes de antecedentes del funcionario afectos al proceso calificatorio. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir informes de evaluaciones anteriores que han tenido los funcionarios. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-06 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar o ingresar las precalificaciones. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-07 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir nómina de notificación de precalificaciones y calificaciones del proceso.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-08 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar y verificar el estado de solicitudes de apelación.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-09 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir nómina de resultado de apelaciones. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir informe de estado de avance del proceso de calificaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mantener o actualizar las precalificaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar y acceder al informe con resultados del proceso.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar resultados en hoja de vida del funcionario.   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-02-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El ingreso y acceso a antecedentes del funcionario, informes de desempeño y de calificaciones.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceso Calificatorio FONASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-02 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar y emitir acta y/o bitácoras de la junta calificadora </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir formulario de precalificaciones en blanco. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-06 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar auto-evaluaciones realizados por parte de los funcionarios </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-07 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-08 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-09 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantener o actualizar las precalificaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-03-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceso Calificatorio Ley Médica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-01 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-02 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar y acceder a antecedentes para diseñar y programar el proceso calificatorio (Nómina de Integrantes Junta Calificadora por Estamento, Normativa Vigente, Nómina de Personal con Requisito Calificación, Parámetros calificatorios y coeficientes). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-05 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-06 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitir formulario de precalificaciones en blanco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-07 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-08 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-09 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-14 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDE-04-15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar ingreso y acceso a antecedentes del funcionario, informes de desempeño y de calificaciones.  </t>
   </si>
   <si>
     <t xml:space="preserve">Tablas de referencia y Glosario</t>
@@ -2525,7 +2719,7 @@
     <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2789,29 +2983,6 @@
     <font>
       <b val="true"/>
       <sz val="9.5"/>
-      <color rgb="FF0B0B0B"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF132C4C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF52514E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10.5"/>
       <color rgb="FF0B0B0B"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -3281,7 +3452,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="94">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3602,23 +3773,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3638,7 +3797,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3650,11 +3809,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3662,7 +3821,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4122,11 +4281,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="56546458"/>
-        <c:axId val="70072030"/>
+        <c:axId val="44905401"/>
+        <c:axId val="77232298"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56546458"/>
+        <c:axId val="44905401"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4158,7 +4317,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70072030"/>
+        <c:crossAx val="77232298"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4166,7 +4325,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70072030"/>
+        <c:axId val="77232298"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4198,7 +4357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56546458"/>
+        <c:crossAx val="44905401"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4542,11 +4701,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="16110741"/>
-        <c:axId val="49940686"/>
+        <c:axId val="1356457"/>
+        <c:axId val="81112389"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16110741"/>
+        <c:axId val="1356457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4578,7 +4737,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49940686"/>
+        <c:crossAx val="81112389"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4586,7 +4745,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49940686"/>
+        <c:axId val="81112389"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -4618,7 +4777,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16110741"/>
+        <c:crossAx val="1356457"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5067,11 +5226,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="49203321"/>
-        <c:axId val="80667277"/>
+        <c:axId val="51760335"/>
+        <c:axId val="85913880"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49203321"/>
+        <c:axId val="51760335"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5103,7 +5262,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80667277"/>
+        <c:crossAx val="85913880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5111,7 +5270,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80667277"/>
+        <c:axId val="85913880"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -5143,7 +5302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49203321"/>
+        <c:crossAx val="51760335"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5232,9 +5391,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Indicadores!$A$101:$A$103</c:f>
+              <c:f>Indicadores!$A$101:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>AutoAtención</c:v>
                 </c:pt>
@@ -5244,15 +5403,27 @@
                 <c:pt idx="2">
                   <c:v>Licencias Médicas</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>Calificaciones</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FORCAP</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Portal SIRH</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>VALS</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Indicadores!$C$101:$C$103</c:f>
+              <c:f>Indicadores!$C$101:$C$107</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>37</c:v>
                 </c:pt>
@@ -5260,6 +5431,18 @@
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5316,9 +5499,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Indicadores!$A$101:$A$103</c:f>
+              <c:f>Indicadores!$A$101:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>AutoAtención</c:v>
                 </c:pt>
@@ -5328,15 +5511,27 @@
                 <c:pt idx="2">
                   <c:v>Licencias Médicas</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>Calificaciones</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FORCAP</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Portal SIRH</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>VALS</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Indicadores!$D$101:$D$103</c:f>
+              <c:f>Indicadores!$D$101:$D$107</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>9</c:v>
                 </c:pt>
@@ -5344,6 +5539,18 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5400,9 +5607,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Indicadores!$A$101:$A$103</c:f>
+              <c:f>Indicadores!$A$101:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>AutoAtención</c:v>
                 </c:pt>
@@ -5412,15 +5619,27 @@
                 <c:pt idx="2">
                   <c:v>Licencias Médicas</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>Calificaciones</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FORCAP</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Portal SIRH</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>VALS</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Indicadores!$E$101:$E$103</c:f>
+              <c:f>Indicadores!$E$101:$E$107</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>24</c:v>
                 </c:pt>
@@ -5428,6 +5647,18 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -5484,9 +5715,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Indicadores!$A$101:$A$103</c:f>
+              <c:f>Indicadores!$A$101:$A$107</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>AutoAtención</c:v>
                 </c:pt>
@@ -5496,15 +5727,27 @@
                 <c:pt idx="2">
                   <c:v>Licencias Médicas</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>Calificaciones</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FORCAP</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Portal SIRH</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>VALS</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Indicadores!$F$101:$F$103</c:f>
+              <c:f>Indicadores!$F$101:$F$107</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5514,17 +5757,29 @@
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:gapWidth val="60"/>
+        <c:gapWidth val="40"/>
         <c:overlap val="100"/>
-        <c:axId val="21992828"/>
-        <c:axId val="19488972"/>
+        <c:axId val="76365292"/>
+        <c:axId val="58267082"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21992828"/>
+        <c:axId val="76365292"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5556,7 +5811,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19488972"/>
+        <c:crossAx val="58267082"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5564,7 +5819,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19488972"/>
+        <c:axId val="58267082"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -5596,7 +5851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21992828"/>
+        <c:crossAx val="76365292"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5780,8 +6035,8 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>245520</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>139320</xdr:rowOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>19080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5790,7 +6045,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="222120" y="10810800"/>
-        <a:ext cx="5579640" cy="2339640"/>
+        <a:ext cx="5579640" cy="3419640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5816,6 +6071,22 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -6334,8 +6605,8 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="36" t="str">
-        <f aca="false">REPT("█",ROUND((Indicadores!B113)*34,0))&amp;REPT("░",34-ROUND((Indicadores!B113)*34,0))&amp;"   "&amp;TEXT(Indicadores!B113,"0.0%")</f>
-        <v>███████████████████░░░░░░░░░░░░░░░   55.7%</v>
+        <f aca="false">REPT("█",ROUND((Indicadores!B117)*34,0))&amp;REPT("░",34-ROUND((Indicadores!B117)*34,0))&amp;"   "&amp;TEXT(Indicadores!B117,"0.0%")</f>
+        <v>███████████████░░░░░░░░░░░░░░░░░░░   44.7%</v>
       </c>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
@@ -6355,8 +6626,8 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="37" t="str">
-        <f aca="false">REPT("█",ROUND((Indicadores!B114)*34,0))&amp;REPT("░",34-ROUND((Indicadores!B114)*34,0))&amp;"   "&amp;TEXT(Indicadores!B114,"0.0%")</f>
-        <v>█████████████████████░░░░░░░░░░░░░   60.9%</v>
+        <f aca="false">REPT("█",ROUND((Indicadores!B118)*34,0))&amp;REPT("░",34-ROUND((Indicadores!B118)*34,0))&amp;"   "&amp;TEXT(Indicadores!B118,"0.0%")</f>
+        <v>█████████████████░░░░░░░░░░░░░░░░░   48.8%</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="37"/>
@@ -7670,13 +7941,721 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF6B6B66"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="66" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1" s="66" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" s="66" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF6B6B66"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="B2:L54"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="7" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="79" t="s">
+        <v>801</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="80" t="s">
+        <v>802</v>
+      </c>
+      <c r="D4" s="80" t="s">
+        <v>803</v>
+      </c>
+      <c r="F4" s="80" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="61" t="s">
+        <v>805</v>
+      </c>
+      <c r="D5" s="61" t="s">
+        <v>806</v>
+      </c>
+      <c r="F5" s="61" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="61" t="s">
+        <v>808</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>809</v>
+      </c>
+      <c r="F6" s="61" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="61" t="s">
+        <v>811</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>812</v>
+      </c>
+      <c r="F7" s="61" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="61" t="s">
+        <v>814</v>
+      </c>
+      <c r="F8" s="61" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="61" t="s">
+        <v>816</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="61" t="s">
+        <v>818</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="61" t="s">
+        <v>820</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="61" t="s">
+        <v>822</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="61" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="61" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="81" t="s">
+        <v>826</v>
+      </c>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="82" t="s">
+        <v>827</v>
+      </c>
+      <c r="C19" s="83" t="s">
+        <v>828</v>
+      </c>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="72" t="s">
+        <v>829</v>
+      </c>
+      <c r="C20" s="84" t="s">
+        <v>830</v>
+      </c>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="76" t="s">
+        <v>831</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>832</v>
+      </c>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="72" t="s">
+        <v>833</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>834</v>
+      </c>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+    </row>
+    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="76" t="s">
+        <v>835</v>
+      </c>
+      <c r="C23" s="85" t="s">
+        <v>836</v>
+      </c>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="72" t="s">
+        <v>837</v>
+      </c>
+      <c r="C24" s="84" t="s">
+        <v>838</v>
+      </c>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="76" t="s">
+        <v>839</v>
+      </c>
+      <c r="C25" s="85" t="s">
+        <v>840</v>
+      </c>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="72" t="s">
+        <v>841</v>
+      </c>
+      <c r="C26" s="84" t="s">
+        <v>842</v>
+      </c>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+    </row>
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="76" t="s">
+        <v>843</v>
+      </c>
+      <c r="C27" s="85" t="s">
+        <v>844</v>
+      </c>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="72" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="84" t="s">
+        <v>845</v>
+      </c>
+      <c r="D28" s="84"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="76" t="s">
+        <v>846</v>
+      </c>
+      <c r="C29" s="85" t="s">
+        <v>847</v>
+      </c>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="72" t="s">
+        <v>848</v>
+      </c>
+      <c r="C30" s="84" t="s">
+        <v>849</v>
+      </c>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+    </row>
+    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="76" t="s">
+        <v>850</v>
+      </c>
+      <c r="C31" s="85" t="s">
+        <v>851</v>
+      </c>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="72" t="s">
+        <v>852</v>
+      </c>
+      <c r="C32" s="84" t="s">
+        <v>853</v>
+      </c>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+    </row>
+    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="85" t="s">
+        <v>854</v>
+      </c>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="84" t="s">
+        <v>855</v>
+      </c>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="85" t="s">
+        <v>856</v>
+      </c>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="84" t="s">
+        <v>857</v>
+      </c>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="85" t="s">
+        <v>858</v>
+      </c>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="84" t="s">
+        <v>859</v>
+      </c>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+    </row>
+    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="85" t="s">
+        <v>860</v>
+      </c>
+      <c r="D39" s="85"/>
+      <c r="E39" s="85"/>
+      <c r="F39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="84" t="s">
+        <v>861</v>
+      </c>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+    </row>
+    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="85" t="s">
+        <v>862</v>
+      </c>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="72" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="84" t="s">
+        <v>863</v>
+      </c>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="76" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="85" t="s">
+        <v>864</v>
+      </c>
+      <c r="D43" s="85"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="85"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="81" t="s">
+        <v>865</v>
+      </c>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
+    </row>
+    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="45" t="s">
+        <v>866</v>
+      </c>
+      <c r="G46" s="45" t="s">
+        <v>867</v>
+      </c>
+      <c r="H46" s="45" t="s">
+        <v>868</v>
+      </c>
+      <c r="I46" s="45" t="s">
+        <v>839</v>
+      </c>
+      <c r="J46" s="45" t="s">
+        <v>869</v>
+      </c>
+      <c r="K46" s="45" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="76" t="s">
+        <v>870</v>
+      </c>
+      <c r="G47" s="86" t="s">
+        <v>871</v>
+      </c>
+      <c r="H47" s="87" t="s">
+        <v>872</v>
+      </c>
+      <c r="I47" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="J47" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="K47" s="89" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="H48" s="91" t="s">
+        <v>873</v>
+      </c>
+      <c r="I48" s="92" t="s">
+        <v>871</v>
+      </c>
+      <c r="J48" s="91" t="s">
+        <v>873</v>
+      </c>
+      <c r="K48" s="93" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="76" t="s">
+        <v>874</v>
+      </c>
+      <c r="G49" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="H49" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="I49" s="86" t="s">
+        <v>875</v>
+      </c>
+      <c r="J49" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="K49" s="88" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="72" t="s">
+        <v>97</v>
+      </c>
+      <c r="G50" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="H50" s="91" t="s">
+        <v>873</v>
+      </c>
+      <c r="I50" s="92" t="s">
+        <v>871</v>
+      </c>
+      <c r="J50" s="93" t="s">
+        <v>872</v>
+      </c>
+      <c r="K50" s="91" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="76" t="s">
+        <v>876</v>
+      </c>
+      <c r="G51" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="H51" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="I51" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="J51" s="87" t="s">
+        <v>872</v>
+      </c>
+      <c r="K51" s="89" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="72" t="s">
+        <v>877</v>
+      </c>
+      <c r="G52" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="91" t="s">
+        <v>873</v>
+      </c>
+      <c r="I52" s="92" t="s">
+        <v>871</v>
+      </c>
+      <c r="J52" s="91" t="s">
+        <v>873</v>
+      </c>
+      <c r="K52" s="93" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="76" t="s">
+        <v>878</v>
+      </c>
+      <c r="G53" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="H53" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="I53" s="88" t="s">
+        <v>873</v>
+      </c>
+      <c r="J53" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="K53" s="87" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="72" t="s">
+        <v>879</v>
+      </c>
+      <c r="G54" s="92" t="s">
+        <v>871</v>
+      </c>
+      <c r="H54" s="93" t="s">
+        <v>872</v>
+      </c>
+      <c r="I54" s="91" t="s">
+        <v>873</v>
+      </c>
+      <c r="J54" s="93" t="s">
+        <v>872</v>
+      </c>
+      <c r="K54" s="90" t="s">
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="B45:L45"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF132C4C"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -10458,101 +11437,217 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="64" t="s">
+      <c r="A104" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="B104" s="52" t="n">
+        <f aca="false">COUNTA('Req. Calificaciones'!D2:D200)</f>
+        <v>43</v>
+      </c>
+      <c r="C104" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Calificaciones'!I2:I200,"Listo")</f>
+        <v>0</v>
+      </c>
+      <c r="D104" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Calificaciones'!I2:I200,"Maqueta")</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Calificaciones'!I2:I200,"Pendiente")</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Calificaciones'!I2:I200,"Observado")</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="53" t="n">
+        <f aca="false">IF(B104=0,0,C104/B104)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B105" s="55" t="n">
+        <f aca="false">COUNTA('Req. FORCAP'!D2:D200)</f>
+        <v>0</v>
+      </c>
+      <c r="C105" s="55" t="n">
+        <f aca="false">COUNTIF('Req. FORCAP'!I2:I200,"Listo")</f>
+        <v>0</v>
+      </c>
+      <c r="D105" s="55" t="n">
+        <f aca="false">COUNTIF('Req. FORCAP'!I2:I200,"Maqueta")</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="55" t="n">
+        <f aca="false">COUNTIF('Req. FORCAP'!I2:I200,"Pendiente")</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="55" t="n">
+        <f aca="false">COUNTIF('Req. FORCAP'!I2:I200,"Observado")</f>
+        <v>0</v>
+      </c>
+      <c r="G105" s="50" t="n">
+        <f aca="false">IF(B105=0,0,C105/B105)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="B106" s="52" t="n">
+        <f aca="false">COUNTA('Req. Portal'!D2:D200)</f>
+        <v>0</v>
+      </c>
+      <c r="C106" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Portal'!I2:I200,"Listo")</f>
+        <v>0</v>
+      </c>
+      <c r="D106" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Portal'!I2:I200,"Maqueta")</f>
+        <v>0</v>
+      </c>
+      <c r="E106" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Portal'!I2:I200,"Pendiente")</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="52" t="n">
+        <f aca="false">COUNTIF('Req. Portal'!I2:I200,"Observado")</f>
+        <v>0</v>
+      </c>
+      <c r="G106" s="53" t="n">
+        <f aca="false">IF(B106=0,0,C106/B106)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="B107" s="55" t="n">
+        <f aca="false">COUNTA('Req. VALS'!D2:D200)</f>
+        <v>0</v>
+      </c>
+      <c r="C107" s="55" t="n">
+        <f aca="false">COUNTIF('Req. VALS'!I2:I200,"Listo")</f>
+        <v>0</v>
+      </c>
+      <c r="D107" s="55" t="n">
+        <f aca="false">COUNTIF('Req. VALS'!I2:I200,"Maqueta")</f>
+        <v>0</v>
+      </c>
+      <c r="E107" s="55" t="n">
+        <f aca="false">COUNTIF('Req. VALS'!I2:I200,"Pendiente")</f>
+        <v>0</v>
+      </c>
+      <c r="F107" s="55" t="n">
+        <f aca="false">COUNTIF('Req. VALS'!I2:I200,"Observado")</f>
+        <v>0</v>
+      </c>
+      <c r="G107" s="50" t="n">
+        <f aca="false">IF(B107=0,0,C107/B107)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="B104" s="64" t="n">
-        <f aca="false">SUM(B101:B103)</f>
-        <v>174</v>
-      </c>
-      <c r="C104" s="64" t="n">
-        <f aca="false">SUM(C101:C103)</f>
+      <c r="B108" s="64" t="n">
+        <f aca="false">SUM(B101:B107)</f>
+        <v>217</v>
+      </c>
+      <c r="C108" s="64" t="n">
+        <f aca="false">SUM(C101:C107)</f>
         <v>97</v>
       </c>
-      <c r="D104" s="64" t="n">
-        <f aca="false">SUM(D101:D103)</f>
+      <c r="D108" s="64" t="n">
+        <f aca="false">SUM(D101:D107)</f>
         <v>9</v>
       </c>
-      <c r="E104" s="64" t="n">
-        <f aca="false">SUM(E101:E103)</f>
+      <c r="E108" s="64" t="n">
+        <f aca="false">SUM(E101:E107)</f>
         <v>43</v>
       </c>
-      <c r="F104" s="64" t="n">
-        <f aca="false">SUM(F101:F103)</f>
+      <c r="F108" s="64" t="n">
+        <f aca="false">SUM(F101:F107)</f>
         <v>8</v>
       </c>
-      <c r="G104" s="65" t="n">
-        <f aca="false">IF(B104=0,0,C104/B104)</f>
-        <v>0.557471264367816</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="44" t="s">
+      <c r="G108" s="65" t="n">
+        <f aca="false">IF(B108=0,0,C108/B108)</f>
+        <v>0.447004608294931</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="B107" s="44"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="B109" s="47" t="n">
-        <f aca="false">B104</f>
-        <v>174</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="48" t="s">
-        <v>136</v>
-      </c>
-      <c r="B110" s="49" t="n">
-        <f aca="false">C104</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="46" t="s">
-        <v>137</v>
-      </c>
-      <c r="B111" s="47" t="n">
-        <f aca="false">D104</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="B112" s="49" t="n">
-        <f aca="false">E104</f>
-        <v>43</v>
-      </c>
+      <c r="B111" s="44"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="B113" s="50" t="n">
-        <f aca="false">IF(B109=0,0,B110/B109)</f>
-        <v>0.557471264367816</v>
+        <v>135</v>
+      </c>
+      <c r="B113" s="47" t="n">
+        <f aca="false">B108</f>
+        <v>217</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B114" s="49" t="n">
+        <f aca="false">C108</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="B115" s="47" t="n">
+        <f aca="false">D108</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="B116" s="49" t="n">
+        <f aca="false">E108</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="B117" s="50" t="n">
+        <f aca="false">IF(B113=0,0,B114/B113)</f>
+        <v>0.447004608294931</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="B114" s="53" t="n">
-        <f aca="false">IF(B109=0,0,(B110+B111)/B109)</f>
-        <v>0.609195402298851</v>
+      <c r="B118" s="53" t="n">
+        <f aca="false">IF(B113=0,0,(B114+B115)/B113)</f>
+        <v>0.488479262672811</v>
       </c>
     </row>
   </sheetData>
@@ -10563,7 +11658,7 @@
     <mergeCell ref="A36:K36"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A98:G98"/>
-    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A111:B111"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30444,97 +31539,1175 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF898781"/>
+    <tabColor rgb="FF1BAF7A"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:H13"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="79" t="s">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="66" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1" s="66" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" s="66" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="69" t="s">
         <v>734</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="80" t="s">
+      <c r="D2" s="69" t="s">
         <v>735</v>
       </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="80"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="80"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="81" t="s">
+      <c r="E2" s="69" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="81" t="s">
+      <c r="F2" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D3" s="73" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="81" t="s">
+      <c r="E3" s="73" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="81" t="s">
+      <c r="F3" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+    </row>
+    <row r="4" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="D4" s="69" t="s">
         <v>739</v>
       </c>
+      <c r="E4" s="69" t="s">
+        <v>740</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D5" s="73" t="s">
+        <v>741</v>
+      </c>
+      <c r="E5" s="73" t="s">
+        <v>742</v>
+      </c>
+      <c r="F5" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>743</v>
+      </c>
+      <c r="E6" s="69" t="s">
+        <v>744</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="73" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>745</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>746</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+    </row>
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>747</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>748</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="73" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>749</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>750</v>
+      </c>
+      <c r="F9" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>751</v>
+      </c>
+      <c r="E10" s="69" t="s">
+        <v>752</v>
+      </c>
+      <c r="F10" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="73" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>753</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>754</v>
+      </c>
+      <c r="F11" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>755</v>
+      </c>
+      <c r="E12" s="69" t="s">
+        <v>756</v>
+      </c>
+      <c r="F12" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="73" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D13" s="73" t="s">
+        <v>757</v>
+      </c>
+      <c r="E13" s="73" t="s">
+        <v>758</v>
+      </c>
+      <c r="F13" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="69" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>734</v>
+      </c>
+      <c r="D14" s="69" t="s">
+        <v>759</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>760</v>
+      </c>
+      <c r="F14" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+    </row>
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="73" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>734</v>
+      </c>
+      <c r="D15" s="73" t="s">
+        <v>761</v>
+      </c>
+      <c r="E15" s="73" t="s">
+        <v>762</v>
+      </c>
+      <c r="F15" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+    </row>
+    <row r="16" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>764</v>
+      </c>
+      <c r="E16" s="69" t="s">
+        <v>740</v>
+      </c>
+      <c r="F16" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="73" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D17" s="73" t="s">
+        <v>765</v>
+      </c>
+      <c r="E17" s="73" t="s">
+        <v>766</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>767</v>
+      </c>
+      <c r="E18" s="69" t="s">
+        <v>742</v>
+      </c>
+      <c r="F18" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="73" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D19" s="73" t="s">
+        <v>768</v>
+      </c>
+      <c r="E19" s="73" t="s">
+        <v>769</v>
+      </c>
+      <c r="F19" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="73"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="69" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>770</v>
+      </c>
+      <c r="E20" s="69" t="s">
+        <v>746</v>
+      </c>
+      <c r="F20" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+    </row>
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="73" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D21" s="73" t="s">
+        <v>771</v>
+      </c>
+      <c r="E21" s="73" t="s">
+        <v>772</v>
+      </c>
+      <c r="F21" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="73"/>
+    </row>
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="69" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>773</v>
+      </c>
+      <c r="E22" s="69" t="s">
+        <v>748</v>
+      </c>
+      <c r="F22" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D23" s="73" t="s">
+        <v>774</v>
+      </c>
+      <c r="E23" s="73" t="s">
+        <v>750</v>
+      </c>
+      <c r="F23" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="69" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D24" s="69" t="s">
+        <v>775</v>
+      </c>
+      <c r="E24" s="69" t="s">
+        <v>752</v>
+      </c>
+      <c r="F24" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="73" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D25" s="73" t="s">
+        <v>776</v>
+      </c>
+      <c r="E25" s="73" t="s">
+        <v>754</v>
+      </c>
+      <c r="F25" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="69" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D26" s="69" t="s">
+        <v>777</v>
+      </c>
+      <c r="E26" s="69" t="s">
+        <v>778</v>
+      </c>
+      <c r="F26" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D27" s="73" t="s">
+        <v>779</v>
+      </c>
+      <c r="E27" s="73" t="s">
+        <v>758</v>
+      </c>
+      <c r="F27" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="69" t="s">
+        <v>763</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>780</v>
+      </c>
+      <c r="E28" s="69" t="s">
+        <v>760</v>
+      </c>
+      <c r="F28" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+    </row>
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="73" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>763</v>
+      </c>
+      <c r="D29" s="73" t="s">
+        <v>781</v>
+      </c>
+      <c r="E29" s="73" t="s">
+        <v>762</v>
+      </c>
+      <c r="F29" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="73"/>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="69" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>783</v>
+      </c>
+      <c r="E30" s="69" t="s">
+        <v>736</v>
+      </c>
+      <c r="F30" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="73" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>784</v>
+      </c>
+      <c r="E31" s="73" t="s">
+        <v>738</v>
+      </c>
+      <c r="F31" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+    </row>
+    <row r="32" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="69" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D32" s="69" t="s">
+        <v>785</v>
+      </c>
+      <c r="E32" s="69" t="s">
+        <v>786</v>
+      </c>
+      <c r="F32" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+    </row>
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="73" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D33" s="73" t="s">
+        <v>787</v>
+      </c>
+      <c r="E33" s="73" t="s">
+        <v>742</v>
+      </c>
+      <c r="F33" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+    </row>
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="69" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D34" s="69" t="s">
+        <v>788</v>
+      </c>
+      <c r="E34" s="69" t="s">
+        <v>744</v>
+      </c>
+      <c r="F34" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="73" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D35" s="73" t="s">
+        <v>789</v>
+      </c>
+      <c r="E35" s="73" t="s">
+        <v>790</v>
+      </c>
+      <c r="F35" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="73"/>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="69" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D36" s="69" t="s">
+        <v>791</v>
+      </c>
+      <c r="E36" s="69" t="s">
+        <v>746</v>
+      </c>
+      <c r="F36" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+    </row>
+    <row r="37" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="73" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D37" s="73" t="s">
+        <v>792</v>
+      </c>
+      <c r="E37" s="73" t="s">
+        <v>748</v>
+      </c>
+      <c r="F37" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G37" s="73"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="73"/>
+      <c r="K37" s="73"/>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="69" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D38" s="69" t="s">
+        <v>793</v>
+      </c>
+      <c r="E38" s="69" t="s">
+        <v>750</v>
+      </c>
+      <c r="F38" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="73" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D39" s="73" t="s">
+        <v>794</v>
+      </c>
+      <c r="E39" s="73" t="s">
+        <v>752</v>
+      </c>
+      <c r="F39" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="69" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D40" s="69" t="s">
+        <v>795</v>
+      </c>
+      <c r="E40" s="69" t="s">
+        <v>754</v>
+      </c>
+      <c r="F40" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G40" s="69"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="73" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D41" s="73" t="s">
+        <v>796</v>
+      </c>
+      <c r="E41" s="73" t="s">
+        <v>778</v>
+      </c>
+      <c r="F41" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="69" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D42" s="69" t="s">
+        <v>797</v>
+      </c>
+      <c r="E42" s="69" t="s">
+        <v>758</v>
+      </c>
+      <c r="F42" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="69"/>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="73" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>782</v>
+      </c>
+      <c r="D43" s="73" t="s">
+        <v>798</v>
+      </c>
+      <c r="E43" s="73" t="s">
+        <v>760</v>
+      </c>
+      <c r="F43" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73"/>
+      <c r="J43" s="73"/>
+      <c r="K43" s="73"/>
+    </row>
+    <row r="44" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="69" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="69" t="s">
+        <v>782</v>
+      </c>
+      <c r="D44" s="69" t="s">
+        <v>799</v>
+      </c>
+      <c r="E44" s="69" t="s">
+        <v>800</v>
+      </c>
+      <c r="F44" s="69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:H8"/>
-  </mergeCells>
+  <autoFilter ref="A1:K44"/>
+  <conditionalFormatting sqref="I2:I44">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>"COMPLETAR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>"Falta planificación"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>"Programado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>"No iniciado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>"Inicio anticipado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>"En curso"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>"Inicio retrasado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>"Atrasado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>"Finalizado anticipado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>"Finalizado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>"Finalizado con desfase"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>"Listo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>"Maqueta"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>"Pendiente"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>"Observado"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -30542,646 +32715,60 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF6B6B66"/>
+    <tabColor rgb="FFEB6834"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:L54"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="82" t="s">
-        <v>740</v>
-      </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="83" t="s">
-        <v>741</v>
-      </c>
-      <c r="D4" s="83" t="s">
-        <v>742</v>
-      </c>
-      <c r="F4" s="83" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="61" t="s">
-        <v>744</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>745</v>
-      </c>
-      <c r="F5" s="61" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="61" t="s">
-        <v>747</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>748</v>
-      </c>
-      <c r="F6" s="61" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="61" t="s">
-        <v>750</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>751</v>
-      </c>
-      <c r="F7" s="61" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="61" t="s">
-        <v>753</v>
-      </c>
-      <c r="F8" s="61" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="61" t="s">
-        <v>755</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="61" t="s">
-        <v>757</v>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="61" t="s">
-        <v>759</v>
-      </c>
-      <c r="F11" s="61" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="61" t="s">
-        <v>761</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="61" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="61" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="84" t="s">
-        <v>765</v>
-      </c>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="85" t="s">
-        <v>766</v>
-      </c>
-      <c r="C19" s="86" t="s">
-        <v>767</v>
-      </c>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-    </row>
-    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="72" t="s">
-        <v>768</v>
-      </c>
-      <c r="C20" s="87" t="s">
-        <v>769</v>
-      </c>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-    </row>
-    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="76" t="s">
-        <v>770</v>
-      </c>
-      <c r="C21" s="88" t="s">
-        <v>771</v>
-      </c>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-    </row>
-    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="72" t="s">
-        <v>772</v>
-      </c>
-      <c r="C22" s="87" t="s">
-        <v>773</v>
-      </c>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="87"/>
-    </row>
-    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="76" t="s">
-        <v>774</v>
-      </c>
-      <c r="C23" s="88" t="s">
-        <v>775</v>
-      </c>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-    </row>
-    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="72" t="s">
-        <v>776</v>
-      </c>
-      <c r="C24" s="87" t="s">
-        <v>777</v>
-      </c>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-    </row>
-    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="76" t="s">
-        <v>778</v>
-      </c>
-      <c r="C25" s="88" t="s">
-        <v>779</v>
-      </c>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-    </row>
-    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="72" t="s">
-        <v>780</v>
-      </c>
-      <c r="C26" s="87" t="s">
-        <v>781</v>
-      </c>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-    </row>
-    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="76" t="s">
-        <v>782</v>
-      </c>
-      <c r="C27" s="88" t="s">
-        <v>783</v>
-      </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-    </row>
-    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="87" t="s">
-        <v>784</v>
-      </c>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="87"/>
-    </row>
-    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="76" t="s">
-        <v>785</v>
-      </c>
-      <c r="C29" s="88" t="s">
-        <v>786</v>
-      </c>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-    </row>
-    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="72" t="s">
-        <v>787</v>
-      </c>
-      <c r="C30" s="87" t="s">
-        <v>788</v>
-      </c>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-    </row>
-    <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="76" t="s">
-        <v>789</v>
-      </c>
-      <c r="C31" s="88" t="s">
-        <v>790</v>
-      </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-    </row>
-    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="72" t="s">
-        <v>791</v>
-      </c>
-      <c r="C32" s="87" t="s">
-        <v>792</v>
-      </c>
-      <c r="D32" s="87"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="87"/>
-    </row>
-    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="76" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="88" t="s">
-        <v>793</v>
-      </c>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-    </row>
-    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="87" t="s">
-        <v>794</v>
-      </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="87"/>
-    </row>
-    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="76" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="88" t="s">
-        <v>795</v>
-      </c>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-    </row>
-    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="72" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="87" t="s">
-        <v>796</v>
-      </c>
-      <c r="D36" s="87"/>
-      <c r="E36" s="87"/>
-      <c r="F36" s="87"/>
-    </row>
-    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="76" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="88" t="s">
-        <v>797</v>
-      </c>
-      <c r="D37" s="88"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-    </row>
-    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="87" t="s">
-        <v>798</v>
-      </c>
-      <c r="D38" s="87"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="87"/>
-    </row>
-    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="88" t="s">
-        <v>799</v>
-      </c>
-      <c r="D39" s="88"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
-    </row>
-    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="87" t="s">
-        <v>800</v>
-      </c>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="87"/>
-    </row>
-    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41" s="88" t="s">
-        <v>801</v>
-      </c>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
-    </row>
-    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="87" t="s">
-        <v>802</v>
-      </c>
-      <c r="D42" s="87"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="87"/>
-    </row>
-    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="76" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="88" t="s">
-        <v>803</v>
-      </c>
-      <c r="D43" s="88"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="88"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="84" t="s">
-        <v>804</v>
-      </c>
-      <c r="C45" s="84"/>
-      <c r="D45" s="84"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="84"/>
-      <c r="G45" s="84"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="84"/>
-      <c r="L45" s="84"/>
-    </row>
-    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="45" t="s">
-        <v>805</v>
-      </c>
-      <c r="G46" s="45" t="s">
-        <v>806</v>
-      </c>
-      <c r="H46" s="45" t="s">
-        <v>807</v>
-      </c>
-      <c r="I46" s="45" t="s">
-        <v>778</v>
-      </c>
-      <c r="J46" s="45" t="s">
-        <v>808</v>
-      </c>
-      <c r="K46" s="45" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="76" t="s">
-        <v>809</v>
-      </c>
-      <c r="G47" s="89" t="s">
-        <v>810</v>
-      </c>
-      <c r="H47" s="90" t="s">
-        <v>811</v>
-      </c>
-      <c r="I47" s="91" t="s">
-        <v>812</v>
-      </c>
-      <c r="J47" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="K47" s="92" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="72" t="s">
-        <v>176</v>
-      </c>
-      <c r="G48" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="H48" s="94" t="s">
-        <v>812</v>
-      </c>
-      <c r="I48" s="95" t="s">
-        <v>810</v>
-      </c>
-      <c r="J48" s="94" t="s">
-        <v>812</v>
-      </c>
-      <c r="K48" s="96" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="76" t="s">
-        <v>813</v>
-      </c>
-      <c r="G49" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="H49" s="91" t="s">
-        <v>812</v>
-      </c>
-      <c r="I49" s="89" t="s">
-        <v>814</v>
-      </c>
-      <c r="J49" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="K49" s="91" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="72" t="s">
-        <v>97</v>
-      </c>
-      <c r="G50" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="H50" s="94" t="s">
-        <v>812</v>
-      </c>
-      <c r="I50" s="95" t="s">
-        <v>810</v>
-      </c>
-      <c r="J50" s="96" t="s">
-        <v>811</v>
-      </c>
-      <c r="K50" s="94" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="76" t="s">
-        <v>815</v>
-      </c>
-      <c r="G51" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="H51" s="91" t="s">
-        <v>812</v>
-      </c>
-      <c r="I51" s="91" t="s">
-        <v>812</v>
-      </c>
-      <c r="J51" s="90" t="s">
-        <v>811</v>
-      </c>
-      <c r="K51" s="92" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="72" t="s">
-        <v>816</v>
-      </c>
-      <c r="G52" s="93" t="s">
-        <v>155</v>
-      </c>
-      <c r="H52" s="94" t="s">
-        <v>812</v>
-      </c>
-      <c r="I52" s="95" t="s">
-        <v>810</v>
-      </c>
-      <c r="J52" s="94" t="s">
-        <v>812</v>
-      </c>
-      <c r="K52" s="96" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="76" t="s">
-        <v>817</v>
-      </c>
-      <c r="G53" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="H53" s="91" t="s">
-        <v>812</v>
-      </c>
-      <c r="I53" s="91" t="s">
-        <v>812</v>
-      </c>
-      <c r="J53" s="92" t="s">
-        <v>155</v>
-      </c>
-      <c r="K53" s="90" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="72" t="s">
-        <v>818</v>
-      </c>
-      <c r="G54" s="95" t="s">
-        <v>810</v>
-      </c>
-      <c r="H54" s="96" t="s">
-        <v>811</v>
-      </c>
-      <c r="I54" s="94" t="s">
-        <v>812</v>
-      </c>
-      <c r="J54" s="96" t="s">
-        <v>811</v>
-      </c>
-      <c r="K54" s="93" t="s">
-        <v>155</v>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="66" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1" s="66" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" s="66" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="B45:L45"/>
-  </mergeCells>
+  <autoFilter ref="A1:K1"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -31189,5 +32776,67 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF4A3AA7"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="66" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" s="66" t="s">
+        <v>697</v>
+      </c>
+      <c r="F1" s="66" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1" s="66" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1" s="66" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1" s="66" t="s">
+        <v>475</v>
+      </c>
+      <c r="J1" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>